--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/26.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/26.xlsx
@@ -426,13 +426,13 @@
         <v>-4.505398966854007</v>
       </c>
       <c r="E2">
-        <v>-25.19605559204284</v>
+        <v>-24.77484411069338</v>
       </c>
       <c r="F2">
-        <v>-5.524010419553553</v>
+        <v>-5.142207599929233</v>
       </c>
       <c r="G2">
-        <v>-15.92759466635121</v>
+        <v>-15.59424880568411</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.789072524331495</v>
       </c>
       <c r="E3">
-        <v>-26.07762721253805</v>
+        <v>-25.53287896025935</v>
       </c>
       <c r="F3">
-        <v>-5.350409462948861</v>
+        <v>-4.579195269105508</v>
       </c>
       <c r="G3">
-        <v>-16.04546598843115</v>
+        <v>-15.69349099236029</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.111990330931795</v>
       </c>
       <c r="E4">
-        <v>-26.33717217181367</v>
+        <v>-24.11082491000066</v>
       </c>
       <c r="F4">
-        <v>-5.398413353941093</v>
+        <v>-4.395089785465915</v>
       </c>
       <c r="G4">
-        <v>-15.96037078850851</v>
+        <v>-15.65901519743521</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.413773392124319</v>
       </c>
       <c r="E5">
-        <v>-26.44098743843951</v>
+        <v>-26.01964463134383</v>
       </c>
       <c r="F5">
-        <v>-5.430887012865639</v>
+        <v>-4.886275207160298</v>
       </c>
       <c r="G5">
-        <v>-15.65132401409987</v>
+        <v>-16.30640021111365</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.676291415897972</v>
       </c>
       <c r="E6">
-        <v>-26.63002858588971</v>
+        <v>-24.81643814445384</v>
       </c>
       <c r="F6">
-        <v>-5.526243698071501</v>
+        <v>-4.502253191263878</v>
       </c>
       <c r="G6">
-        <v>-15.9078466343957</v>
+        <v>-14.98501127385577</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.865556291991726</v>
       </c>
       <c r="E7">
-        <v>-27.51079413801155</v>
+        <v>-26.90466242055888</v>
       </c>
       <c r="F7">
-        <v>-5.445712304273542</v>
+        <v>-4.618962703011704</v>
       </c>
       <c r="G7">
-        <v>-16.01102792755399</v>
+        <v>-14.84498678441724</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.949948663623339</v>
       </c>
       <c r="E8">
-        <v>-28.1396406810867</v>
+        <v>-26.09728078973134</v>
       </c>
       <c r="F8">
-        <v>-4.9678843069493</v>
+        <v>-3.985132414555245</v>
       </c>
       <c r="G8">
-        <v>-15.56028980315463</v>
+        <v>-16.44078264008071</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.90205858087513</v>
       </c>
       <c r="E9">
-        <v>-28.13939614349028</v>
+        <v>-27.97933270121517</v>
       </c>
       <c r="F9">
-        <v>-5.016461428184269</v>
+        <v>-3.962539522011291</v>
       </c>
       <c r="G9">
-        <v>-15.50241069545681</v>
+        <v>-16.43130319099547</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.69896325231812</v>
       </c>
       <c r="E10">
-        <v>-29.7489154322445</v>
+        <v>-28.23348877642166</v>
       </c>
       <c r="F10">
-        <v>-5.111946510337565</v>
+        <v>-3.690953470431654</v>
       </c>
       <c r="G10">
-        <v>-15.70181052962426</v>
+        <v>-17.41110712025048</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.326884239820509</v>
       </c>
       <c r="E11">
-        <v>-29.81461453314778</v>
+        <v>-29.11634648353505</v>
       </c>
       <c r="F11">
-        <v>-5.021101942374751</v>
+        <v>-3.276506348197811</v>
       </c>
       <c r="G11">
-        <v>-15.05966890799781</v>
+        <v>-16.36193160478569</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.788902074934415</v>
       </c>
       <c r="E12">
-        <v>-30.22375310279278</v>
+        <v>-28.5290034047402</v>
       </c>
       <c r="F12">
-        <v>-4.976529149164915</v>
+        <v>-3.681607001025867</v>
       </c>
       <c r="G12">
-        <v>-14.65165064769164</v>
+        <v>-15.4476454670189</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.096665836203311</v>
       </c>
       <c r="E13">
-        <v>-30.93844819186834</v>
+        <v>-29.96205032565251</v>
       </c>
       <c r="F13">
-        <v>-4.934996464323354</v>
+        <v>-3.405517115877208</v>
       </c>
       <c r="G13">
-        <v>-14.28502991919021</v>
+        <v>-14.78848414916361</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.285730556747421</v>
       </c>
       <c r="E14">
-        <v>-31.87740463498875</v>
+        <v>-30.77394910930271</v>
       </c>
       <c r="F14">
-        <v>-4.757005160483824</v>
+        <v>-2.935100521705814</v>
       </c>
       <c r="G14">
-        <v>-13.99581976971919</v>
+        <v>-12.40907352311668</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.39874122236446</v>
       </c>
       <c r="E15">
-        <v>-32.37935201518395</v>
+        <v>-32.13993159439841</v>
       </c>
       <c r="F15">
-        <v>-4.748762904825969</v>
+        <v>-2.870225271820765</v>
       </c>
       <c r="G15">
-        <v>-13.04113523211251</v>
+        <v>-13.93320421870031</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.489491297277296</v>
       </c>
       <c r="E16">
-        <v>-32.9875396598361</v>
+        <v>-31.16976943689115</v>
       </c>
       <c r="F16">
-        <v>-4.45804073787426</v>
+        <v>-2.90136111738979</v>
       </c>
       <c r="G16">
-        <v>-13.00674146772641</v>
+        <v>-14.05974780936185</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.6137107642523313</v>
       </c>
       <c r="E17">
-        <v>-33.6104584304352</v>
+        <v>-33.48902966415653</v>
       </c>
       <c r="F17">
-        <v>-4.569294621907248</v>
+        <v>-2.843124403870776</v>
       </c>
       <c r="G17">
-        <v>-12.86713533403672</v>
+        <v>-13.10158845812372</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.1835519520054697</v>
       </c>
       <c r="E18">
-        <v>-34.62533926876822</v>
+        <v>-35.38265182672995</v>
       </c>
       <c r="F18">
-        <v>-4.379307729707778</v>
+        <v>-2.690426470308327</v>
       </c>
       <c r="G18">
-        <v>-12.18314173141955</v>
+        <v>-11.73786355969511</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.8624824435819469</v>
       </c>
       <c r="E19">
-        <v>-35.57486064174852</v>
+        <v>-35.06636735237523</v>
       </c>
       <c r="F19">
-        <v>-4.28925756608425</v>
+        <v>-2.883905759477999</v>
       </c>
       <c r="G19">
-        <v>-11.72200213467675</v>
+        <v>-11.13717032880756</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.406157224474119</v>
       </c>
       <c r="E20">
-        <v>-35.83702985171158</v>
+        <v>-33.75724891539384</v>
       </c>
       <c r="F20">
-        <v>-3.941108000566063</v>
+        <v>-2.146394521784946</v>
       </c>
       <c r="G20">
-        <v>-11.67752845766004</v>
+        <v>-11.14494026146033</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.805745167949034</v>
       </c>
       <c r="E21">
-        <v>-36.39784060129548</v>
+        <v>-35.3416442303535</v>
       </c>
       <c r="F21">
-        <v>-3.687799875729196</v>
+        <v>-1.924821152149329</v>
       </c>
       <c r="G21">
-        <v>-11.48386091755693</v>
+        <v>-11.66384576375715</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.069167284527799</v>
       </c>
       <c r="E22">
-        <v>-37.65062708585847</v>
+        <v>-36.64126872157781</v>
       </c>
       <c r="F22">
-        <v>-3.656213398293048</v>
+        <v>-2.936468156287836</v>
       </c>
       <c r="G22">
-        <v>-11.05803710845843</v>
+        <v>-10.45425952930501</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.212760912878514</v>
       </c>
       <c r="E23">
-        <v>-36.983804759755</v>
+        <v>-36.11994400110378</v>
       </c>
       <c r="F23">
-        <v>-3.829474724262593</v>
+        <v>-1.267591969665993</v>
       </c>
       <c r="G23">
-        <v>-11.26738560639413</v>
+        <v>-10.90045316184454</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.254441301327208</v>
       </c>
       <c r="E24">
-        <v>-38.56453653924245</v>
+        <v>-37.35909977890368</v>
       </c>
       <c r="F24">
-        <v>-3.586077187032819</v>
+        <v>-1.827720753560573</v>
       </c>
       <c r="G24">
-        <v>-10.60991083642039</v>
+        <v>-10.16530203389407</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.217764057627171</v>
       </c>
       <c r="E25">
-        <v>-38.12846939891084</v>
+        <v>-39.65820376836091</v>
       </c>
       <c r="F25">
-        <v>-3.425852707248533</v>
+        <v>-1.755202157649894</v>
       </c>
       <c r="G25">
-        <v>-10.81962026872762</v>
+        <v>-10.25621155842005</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.118318896239044</v>
       </c>
       <c r="E26">
-        <v>-37.91849538036018</v>
+        <v>-37.56131199300518</v>
       </c>
       <c r="F26">
-        <v>-3.380299127033783</v>
+        <v>-1.307431471536232</v>
       </c>
       <c r="G26">
-        <v>-11.10536872945342</v>
+        <v>-11.40756595385672</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.972721531200645</v>
       </c>
       <c r="E27">
-        <v>-38.15775956879245</v>
+        <v>-37.10095411809642</v>
       </c>
       <c r="F27">
-        <v>-3.427020705286481</v>
+        <v>-1.962207858139879</v>
       </c>
       <c r="G27">
-        <v>-11.41036811706849</v>
+        <v>-10.35840848511051</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.791560227893154</v>
       </c>
       <c r="E28">
-        <v>-37.97372012088372</v>
+        <v>-39.07809039831931</v>
       </c>
       <c r="F28">
-        <v>-3.084621666278528</v>
+        <v>-1.657446520445524</v>
       </c>
       <c r="G28">
-        <v>-11.46568951256073</v>
+        <v>-10.24562633766928</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.583703110544324</v>
       </c>
       <c r="E29">
-        <v>-39.08732848529496</v>
+        <v>-38.53859291165251</v>
       </c>
       <c r="F29">
-        <v>-3.326270519920991</v>
+        <v>-1.617465367749406</v>
       </c>
       <c r="G29">
-        <v>-11.27423351578869</v>
+        <v>-9.380712740707448</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.355196575729192</v>
       </c>
       <c r="E30">
-        <v>-38.29566292351103</v>
+        <v>-37.5148589066345</v>
       </c>
       <c r="F30">
-        <v>-3.465524050536005</v>
+        <v>-1.863048138187764</v>
       </c>
       <c r="G30">
-        <v>-10.85328232070596</v>
+        <v>-10.26376164922833</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.11292359504833</v>
       </c>
       <c r="E31">
-        <v>-37.99233894176626</v>
+        <v>-37.88278609857269</v>
       </c>
       <c r="F31">
-        <v>-3.390927080811701</v>
+        <v>-1.943201796450047</v>
       </c>
       <c r="G31">
-        <v>-11.1813749456564</v>
+        <v>-12.07071067468518</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.862035455378619</v>
       </c>
       <c r="E32">
-        <v>-37.28798462308722</v>
+        <v>-38.75032850659215</v>
       </c>
       <c r="F32">
-        <v>-3.215630456133478</v>
+        <v>-2.426641982928255</v>
       </c>
       <c r="G32">
-        <v>-10.83844791803572</v>
+        <v>-9.871110990095818</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.6105145176226978</v>
       </c>
       <c r="E33">
-        <v>-37.58704957502778</v>
+        <v>-38.24538327660387</v>
       </c>
       <c r="F33">
-        <v>-3.147471557863732</v>
+        <v>-2.281033217598964</v>
       </c>
       <c r="G33">
-        <v>-11.52622805033248</v>
+        <v>-10.11655620640696</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.366494018059565</v>
       </c>
       <c r="E34">
-        <v>-37.15742645320908</v>
+        <v>-36.58477600833212</v>
       </c>
       <c r="F34">
-        <v>-3.495283149481577</v>
+        <v>-2.508623019681114</v>
       </c>
       <c r="G34">
-        <v>-11.15598157200786</v>
+        <v>-9.786524379514892</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.1389873881739818</v>
       </c>
       <c r="E35">
-        <v>-36.77405716490473</v>
+        <v>-36.51987618309119</v>
       </c>
       <c r="F35">
-        <v>-3.228885162945673</v>
+        <v>-1.541508218749705</v>
       </c>
       <c r="G35">
-        <v>-11.3754395135682</v>
+        <v>-11.0708798096421</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.06197055966177395</v>
       </c>
       <c r="E36">
-        <v>-36.32697677578646</v>
+        <v>-36.70226953069813</v>
       </c>
       <c r="F36">
-        <v>-3.090599165457129</v>
+        <v>-1.984281364322277</v>
       </c>
       <c r="G36">
-        <v>-11.95633385356605</v>
+        <v>-12.27807403357741</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.2300054463391025</v>
       </c>
       <c r="E37">
-        <v>-35.23331860361601</v>
+        <v>-36.80164010008544</v>
       </c>
       <c r="F37">
-        <v>-3.202968860381687</v>
+        <v>-2.064999969153269</v>
       </c>
       <c r="G37">
-        <v>-11.50793852136014</v>
+        <v>-10.77345348138623</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.3568379662137308</v>
       </c>
       <c r="E38">
-        <v>-35.9705270012207</v>
+        <v>-35.74314326434756</v>
       </c>
       <c r="F38">
-        <v>-3.044990084626391</v>
+        <v>-1.652640332774481</v>
       </c>
       <c r="G38">
-        <v>-11.50691149901203</v>
+        <v>-10.40525120409315</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.4398082626282993</v>
       </c>
       <c r="E39">
-        <v>-34.57519094760728</v>
+        <v>-35.12831461256316</v>
       </c>
       <c r="F39">
-        <v>-3.319019820044287</v>
+        <v>-1.40581086939491</v>
       </c>
       <c r="G39">
-        <v>-11.46688715842992</v>
+        <v>-11.73700716086809</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.4772456736820568</v>
       </c>
       <c r="E40">
-        <v>-34.09255750905479</v>
+        <v>-34.13309640837145</v>
       </c>
       <c r="F40">
-        <v>-3.006004629548438</v>
+        <v>-1.801641262618237</v>
       </c>
       <c r="G40">
-        <v>-12.13528183375349</v>
+        <v>-10.85836493290154</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.4721472783254645</v>
       </c>
       <c r="E41">
-        <v>-34.55176288732859</v>
+        <v>-35.01771569187382</v>
       </c>
       <c r="F41">
-        <v>-3.042514094459423</v>
+        <v>-1.904978439382669</v>
       </c>
       <c r="G41">
-        <v>-12.01371585619762</v>
+        <v>-10.92673246531414</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.4308706117622985</v>
       </c>
       <c r="E42">
-        <v>-33.86482507968305</v>
+        <v>-32.05292828752605</v>
       </c>
       <c r="F42">
-        <v>-3.002864288724425</v>
+        <v>-1.556196001168743</v>
       </c>
       <c r="G42">
-        <v>-12.30039946506787</v>
+        <v>-11.11258413566264</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.3615904029188305</v>
       </c>
       <c r="E43">
-        <v>-32.8376403774712</v>
+        <v>-33.78433145419671</v>
       </c>
       <c r="F43">
-        <v>-3.255319195136408</v>
+        <v>-1.66994409945156</v>
       </c>
       <c r="G43">
-        <v>-11.65729972674606</v>
+        <v>-11.39737776091465</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.2750011022327499</v>
       </c>
       <c r="E44">
-        <v>-32.27645376454466</v>
+        <v>-30.78515028976068</v>
       </c>
       <c r="F44">
-        <v>-2.803979902251486</v>
+        <v>-1.517921285322392</v>
       </c>
       <c r="G44">
-        <v>-12.20998868621893</v>
+        <v>-11.53884434722855</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.1822106117928577</v>
       </c>
       <c r="E45">
-        <v>-32.03811791328396</v>
+        <v>-30.99127963387882</v>
       </c>
       <c r="F45">
-        <v>-3.269865326729567</v>
+        <v>-2.015558032349778</v>
       </c>
       <c r="G45">
-        <v>-12.73192931845824</v>
+        <v>-11.52346526177943</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.09394237194277708</v>
       </c>
       <c r="E46">
-        <v>-30.75504273032068</v>
+        <v>-28.64910759237164</v>
       </c>
       <c r="F46">
-        <v>-2.86575291621305</v>
+        <v>-1.949472537689239</v>
       </c>
       <c r="G46">
-        <v>-12.18854590332796</v>
+        <v>-11.59987834945578</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.02037759586213639</v>
       </c>
       <c r="E47">
-        <v>-30.56739861710185</v>
+        <v>-30.42840616438442</v>
       </c>
       <c r="F47">
-        <v>-2.94952736839297</v>
+        <v>-1.906949125433929</v>
       </c>
       <c r="G47">
-        <v>-12.39806502478474</v>
+        <v>-11.71416329637124</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.03099066931056323</v>
       </c>
       <c r="E48">
-        <v>-29.8473961564893</v>
+        <v>-28.69769811847394</v>
       </c>
       <c r="F48">
-        <v>-2.944854547873778</v>
+        <v>-1.244620513218959</v>
       </c>
       <c r="G48">
-        <v>-12.92095721127629</v>
+        <v>-11.32286778174278</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.05567866380447629</v>
       </c>
       <c r="E49">
-        <v>-29.69644400391762</v>
+        <v>-27.13492626690091</v>
       </c>
       <c r="F49">
-        <v>-2.965698756830422</v>
+        <v>-1.127539064507277</v>
       </c>
       <c r="G49">
-        <v>-12.6965839998199</v>
+        <v>-11.69106349659275</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.05160566281474757</v>
       </c>
       <c r="E50">
-        <v>-28.49684218233773</v>
+        <v>-27.16180728861044</v>
       </c>
       <c r="F50">
-        <v>-2.670150521390003</v>
+        <v>-1.912969699717476</v>
       </c>
       <c r="G50">
-        <v>-12.44842193205754</v>
+        <v>-12.80272167360326</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.02084735962161488</v>
       </c>
       <c r="E51">
-        <v>-28.78815891525116</v>
+        <v>-27.82325884454081</v>
       </c>
       <c r="F51">
-        <v>-2.855302233059332</v>
+        <v>-2.114135410017725</v>
       </c>
       <c r="G51">
-        <v>-12.69055311459364</v>
+        <v>-12.09398766042788</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.03300430077858332</v>
       </c>
       <c r="E52">
-        <v>-27.7651041813343</v>
+        <v>-24.56303379593262</v>
       </c>
       <c r="F52">
-        <v>-2.593761792973444</v>
+        <v>-1.243723391321727</v>
       </c>
       <c r="G52">
-        <v>-13.02999220369664</v>
+        <v>-11.68703087529619</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.1031639535072106</v>
       </c>
       <c r="E53">
-        <v>-27.68382260137063</v>
+        <v>-26.69830438850335</v>
       </c>
       <c r="F53">
-        <v>-2.720207935173775</v>
+        <v>-1.977643656323645</v>
       </c>
       <c r="G53">
-        <v>-13.0031255615679</v>
+        <v>-13.15269676513363</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.1819243996510766</v>
       </c>
       <c r="E54">
-        <v>-26.85331405378591</v>
+        <v>-25.19268640738113</v>
       </c>
       <c r="F54">
-        <v>-2.906331321806587</v>
+        <v>-1.621815124981506</v>
       </c>
       <c r="G54">
-        <v>-13.2138817035526</v>
+        <v>-11.65959986305923</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.2609501081234176</v>
       </c>
       <c r="E55">
-        <v>-26.32257690008694</v>
+        <v>-25.31224717813164</v>
       </c>
       <c r="F55">
-        <v>-2.997792195117083</v>
+        <v>-1.476712492135325</v>
       </c>
       <c r="G55">
-        <v>-13.13662862315703</v>
+        <v>-12.76310748571608</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.3323760090213769</v>
       </c>
       <c r="E56">
-        <v>-25.98633770501742</v>
+        <v>-24.13485752155937</v>
       </c>
       <c r="F56">
-        <v>-2.89842869678388</v>
+        <v>-1.65993079428652</v>
       </c>
       <c r="G56">
-        <v>-13.19335766269827</v>
+        <v>-12.49571089717226</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.3907696208015153</v>
       </c>
       <c r="E57">
-        <v>-25.57436431064362</v>
+        <v>-23.88571446707937</v>
       </c>
       <c r="F57">
-        <v>-3.030093553621847</v>
+        <v>-1.380886122612075</v>
       </c>
       <c r="G57">
-        <v>-13.64990683047941</v>
+        <v>-12.35751240753156</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.4327849025455313</v>
       </c>
       <c r="E58">
-        <v>-24.58301795172847</v>
+        <v>-21.68360812662943</v>
       </c>
       <c r="F58">
-        <v>-2.707492495540802</v>
+        <v>-1.398597446051332</v>
       </c>
       <c r="G58">
-        <v>-13.73717912090674</v>
+        <v>-13.43412713828721</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.4584849384435274</v>
       </c>
       <c r="E59">
-        <v>-24.68018089003704</v>
+        <v>-23.19109636751682</v>
       </c>
       <c r="F59">
-        <v>-3.031250782883558</v>
+        <v>-1.227713534527821</v>
       </c>
       <c r="G59">
-        <v>-13.92748176830063</v>
+        <v>-11.97392448234624</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.4698013539555921</v>
       </c>
       <c r="E60">
-        <v>-24.34120196819288</v>
+        <v>-19.90155850665698</v>
       </c>
       <c r="F60">
-        <v>-2.89865069924783</v>
+        <v>-1.601894545678983</v>
       </c>
       <c r="G60">
-        <v>-13.67269163298819</v>
+        <v>-12.53474430884341</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.470719084906986</v>
       </c>
       <c r="E61">
-        <v>-23.78326227112984</v>
+        <v>-22.96595875375148</v>
       </c>
       <c r="F61">
-        <v>-3.06157482839784</v>
+        <v>-2.440892387358615</v>
       </c>
       <c r="G61">
-        <v>-14.33136076760957</v>
+        <v>-13.2015508729322</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.465831917317114</v>
       </c>
       <c r="E62">
-        <v>-23.71337433176946</v>
+        <v>-22.52009425990427</v>
       </c>
       <c r="F62">
-        <v>-3.161839590465289</v>
+        <v>-1.608084935280104</v>
       </c>
       <c r="G62">
-        <v>-14.26242886508875</v>
+        <v>-13.00907441625518</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.4593226265688281</v>
       </c>
       <c r="E63">
-        <v>-24.06757798322741</v>
+        <v>-20.86686614002803</v>
       </c>
       <c r="F63">
-        <v>-3.206810000028469</v>
+        <v>-1.974829692256335</v>
       </c>
       <c r="G63">
-        <v>-13.97132545077793</v>
+        <v>-13.40566910370214</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.4549791061181473</v>
       </c>
       <c r="E64">
-        <v>-22.66166341433206</v>
+        <v>-21.57808562530269</v>
       </c>
       <c r="F64">
-        <v>-3.000240020792356</v>
+        <v>-1.662658608143938</v>
       </c>
       <c r="G64">
-        <v>-14.57881409151509</v>
+        <v>-13.57742792745283</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.4547438304968567</v>
       </c>
       <c r="E65">
-        <v>-22.75660287190287</v>
+        <v>-20.4605488096898</v>
       </c>
       <c r="F65">
-        <v>-3.241687581155939</v>
+        <v>-2.235151603892704</v>
       </c>
       <c r="G65">
-        <v>-14.38661653867062</v>
+        <v>-13.11297101571344</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.4586601617354846</v>
       </c>
       <c r="E66">
-        <v>-22.95770787410951</v>
+        <v>-19.52593970161676</v>
       </c>
       <c r="F66">
-        <v>-3.361750324150297</v>
+        <v>-1.933920768069081</v>
       </c>
       <c r="G66">
-        <v>-14.81239769188884</v>
+        <v>-13.35370111664366</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.4651137035013193</v>
       </c>
       <c r="E67">
-        <v>-22.18462037694205</v>
+        <v>-19.37701630540051</v>
       </c>
       <c r="F67">
-        <v>-3.567708968243143</v>
+        <v>-2.851664043426237</v>
       </c>
       <c r="G67">
-        <v>-14.57604802174048</v>
+        <v>-13.19488999316653</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.470324181345042</v>
       </c>
       <c r="E68">
-        <v>-22.19010888743934</v>
+        <v>-20.0511158892343</v>
       </c>
       <c r="F68">
-        <v>-3.531152286390198</v>
+        <v>-2.631452509800821</v>
       </c>
       <c r="G68">
-        <v>-14.74027316079069</v>
+        <v>-13.67757737189021</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.4697538656500376</v>
       </c>
       <c r="E69">
-        <v>-21.64823621615552</v>
+        <v>-19.2960653040394</v>
       </c>
       <c r="F69">
-        <v>-3.720116973214613</v>
+        <v>-3.182665575339072</v>
       </c>
       <c r="G69">
-        <v>-14.76875252331589</v>
+        <v>-12.67799916090721</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.458611335059688</v>
       </c>
       <c r="E70">
-        <v>-21.77653241326682</v>
+        <v>-21.01333057485811</v>
       </c>
       <c r="F70">
-        <v>-3.692070109690627</v>
+        <v>-3.085563520015511</v>
       </c>
       <c r="G70">
-        <v>-14.65056292274469</v>
+        <v>-11.10502420118968</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.4320651237848047</v>
       </c>
       <c r="E71">
-        <v>-21.60444134402734</v>
+        <v>-19.17570752186353</v>
       </c>
       <c r="F71">
-        <v>-3.932628003463604</v>
+        <v>-2.723878431135579</v>
       </c>
       <c r="G71">
-        <v>-14.69292185246634</v>
+        <v>-13.6980718817505</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.3870797060736619</v>
       </c>
       <c r="E72">
-        <v>-21.77219866364148</v>
+        <v>-18.82056194781198</v>
       </c>
       <c r="F72">
-        <v>-3.829545135491831</v>
+        <v>-2.973833324725913</v>
       </c>
       <c r="G72">
-        <v>-14.27793263695713</v>
+        <v>-12.89575742969975</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.3216610014723089</v>
       </c>
       <c r="E73">
-        <v>-21.16607600313683</v>
+        <v>-18.68132948597215</v>
       </c>
       <c r="F73">
-        <v>-4.275518264341417</v>
+        <v>-2.953723877655552</v>
       </c>
       <c r="G73">
-        <v>-14.17357994770211</v>
+        <v>-12.7488177658247</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.2368992395388721</v>
       </c>
       <c r="E74">
-        <v>-21.7429266076559</v>
+        <v>-20.01615154142108</v>
       </c>
       <c r="F74">
-        <v>-4.066872396393889</v>
+        <v>-3.467666208639644</v>
       </c>
       <c r="G74">
-        <v>-14.29077041630845</v>
+        <v>-11.80260206106295</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.1364887387092063</v>
       </c>
       <c r="E75">
-        <v>-22.37036026684065</v>
+        <v>-19.63497629877345</v>
       </c>
       <c r="F75">
-        <v>-4.071860824893547</v>
+        <v>-3.556767063219564</v>
       </c>
       <c r="G75">
-        <v>-14.1056996766911</v>
+        <v>-12.75938329924611</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.02679601128843608</v>
       </c>
       <c r="E76">
-        <v>-22.65310912693158</v>
+        <v>-18.48743381438573</v>
       </c>
       <c r="F76">
-        <v>-4.194884152985511</v>
+        <v>-4.28099625797613</v>
       </c>
       <c r="G76">
-        <v>-13.66192594505165</v>
+        <v>-12.07089770431407</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.08386076206369719</v>
       </c>
       <c r="E77">
-        <v>-22.43649862972268</v>
+        <v>-19.87354536644553</v>
       </c>
       <c r="F77">
-        <v>-4.21431268205077</v>
+        <v>-3.536309701840028</v>
       </c>
       <c r="G77">
-        <v>-13.42856218652239</v>
+        <v>-11.3605690174608</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>0.1869935787805727</v>
       </c>
       <c r="E78">
-        <v>-23.1577260425543</v>
+        <v>-20.21704823382336</v>
       </c>
       <c r="F78">
-        <v>-4.371374455091168</v>
+        <v>-3.670601311712273</v>
       </c>
       <c r="G78">
-        <v>-13.06775906384585</v>
+        <v>-10.10221070574907</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>0.2740728366158403</v>
       </c>
       <c r="E79">
-        <v>-22.64855348207986</v>
+        <v>-21.88177414920508</v>
       </c>
       <c r="F79">
-        <v>-4.266754137219799</v>
+        <v>-3.846520040309998</v>
       </c>
       <c r="G79">
-        <v>-12.77166163032155</v>
+        <v>-10.81116784199049</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.3383217632238221</v>
       </c>
       <c r="E80">
-        <v>-23.82122446873614</v>
+        <v>-22.40517517501162</v>
       </c>
       <c r="F80">
-        <v>-4.364542080752877</v>
+        <v>-4.115928313987676</v>
       </c>
       <c r="G80">
-        <v>-12.72266971121749</v>
+        <v>-10.82806613302163</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.3738047881839335</v>
       </c>
       <c r="E81">
-        <v>-24.13945845115116</v>
+        <v>-21.51114572252131</v>
       </c>
       <c r="F81">
-        <v>-4.570981177939347</v>
+        <v>-3.576727404157421</v>
       </c>
       <c r="G81">
-        <v>-12.85669448703456</v>
+        <v>-9.988011070594155</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.3777945227402434</v>
       </c>
       <c r="E82">
-        <v>-23.93937688407026</v>
+        <v>-21.27744929288147</v>
       </c>
       <c r="F82">
-        <v>-4.500120145201669</v>
+        <v>-4.118289989453057</v>
       </c>
       <c r="G82">
-        <v>-12.08603397936779</v>
+        <v>-9.621698776919306</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.3491934656226745</v>
       </c>
       <c r="E83">
-        <v>-25.35283136218838</v>
+        <v>-21.03770282196739</v>
       </c>
       <c r="F83">
-        <v>-4.556871595967464</v>
+        <v>-3.608352814861501</v>
       </c>
       <c r="G83">
-        <v>-12.12091664576624</v>
+        <v>-10.0150220864715</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.2900172890917108</v>
       </c>
       <c r="E84">
-        <v>-25.80455570140152</v>
+        <v>-22.43742696689425</v>
       </c>
       <c r="F84">
-        <v>-4.721707597083134</v>
+        <v>-3.915045905339184</v>
       </c>
       <c r="G84">
-        <v>-11.56711207096316</v>
+        <v>-10.05121067905062</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.2049198816292047</v>
       </c>
       <c r="E85">
-        <v>-26.34286446364131</v>
+        <v>-22.93493417832493</v>
       </c>
       <c r="F85">
-        <v>-4.555677090172627</v>
+        <v>-4.772984367683827</v>
       </c>
       <c r="G85">
-        <v>-11.39075297458613</v>
+        <v>-9.902732122264187</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.0997468145298768</v>
       </c>
       <c r="E86">
-        <v>-27.79224785453628</v>
+        <v>-25.45690928030667</v>
       </c>
       <c r="F86">
-        <v>-4.754203621927556</v>
+        <v>-4.511578123117192</v>
       </c>
       <c r="G86">
-        <v>-11.1048929523273</v>
+        <v>-9.577234943567271</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.01741151442210764</v>
       </c>
       <c r="E87">
-        <v>-28.43820297241241</v>
+        <v>-27.52486410675338</v>
       </c>
       <c r="F87">
-        <v>-4.692771066968542</v>
+        <v>-5.00044494445114</v>
       </c>
       <c r="G87">
-        <v>-11.15970903969939</v>
+        <v>-8.359711434162834</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.1397422922072294</v>
       </c>
       <c r="E88">
-        <v>-29.87717087308974</v>
+        <v>-27.39871440632171</v>
       </c>
       <c r="F88">
-        <v>-5.114011630272744</v>
+        <v>-5.005087115376429</v>
       </c>
       <c r="G88">
-        <v>-10.83146219733566</v>
+        <v>-9.844936685716128</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.2597059485890354</v>
       </c>
       <c r="E89">
-        <v>-30.9555499739583</v>
+        <v>-29.26046969730317</v>
       </c>
       <c r="F89">
-        <v>-4.975990710353096</v>
+        <v>-4.800314693404391</v>
       </c>
       <c r="G89">
-        <v>-11.20887486354611</v>
+        <v>-8.780134352574485</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.372281782009491</v>
       </c>
       <c r="E90">
-        <v>-31.49364136944573</v>
+        <v>-30.77336493615572</v>
       </c>
       <c r="F90">
-        <v>-5.093971766064218</v>
+        <v>-4.543405655467555</v>
       </c>
       <c r="G90">
-        <v>-10.99188768182003</v>
+        <v>-8.476424485032283</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.4739272971992827</v>
       </c>
       <c r="E91">
-        <v>-33.11560490477301</v>
+        <v>-33.23243726993391</v>
       </c>
       <c r="F91">
-        <v>-5.160711670972969</v>
+        <v>-4.989726698626318</v>
       </c>
       <c r="G91">
-        <v>-10.56043985896864</v>
+        <v>-8.626563339927793</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.563128996197365</v>
       </c>
       <c r="E92">
-        <v>-34.72559062635002</v>
+        <v>-33.03750457779973</v>
       </c>
       <c r="F92">
-        <v>-5.513233359643132</v>
+        <v>-5.419156502074595</v>
       </c>
       <c r="G92">
-        <v>-10.65507685118615</v>
+        <v>-8.446598181056929</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.6427409350292345</v>
       </c>
       <c r="E93">
-        <v>-35.87605624070969</v>
+        <v>-33.25249388131388</v>
       </c>
       <c r="F93">
-        <v>-5.252446733893792</v>
+        <v>-5.941546523832436</v>
       </c>
       <c r="G93">
-        <v>-10.75169898244711</v>
+        <v>-9.326516804210101</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.7161754475020601</v>
       </c>
       <c r="E94">
-        <v>-37.68413100080421</v>
+        <v>-35.101059991748</v>
       </c>
       <c r="F94">
-        <v>-5.544568841756232</v>
+        <v>-5.853278178492329</v>
       </c>
       <c r="G94">
-        <v>-10.96798070153791</v>
+        <v>-8.623902269243084</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.7916625374561274</v>
       </c>
       <c r="E95">
-        <v>-39.56048156351239</v>
+        <v>-38.99651673178214</v>
       </c>
       <c r="F95">
-        <v>-5.490872409971963</v>
+        <v>-5.839863596771394</v>
       </c>
       <c r="G95">
-        <v>-11.38460068416217</v>
+        <v>-8.942338259144075</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.8786274355257874</v>
       </c>
       <c r="E96">
-        <v>-41.21478293172846</v>
+        <v>-38.90869150687738</v>
       </c>
       <c r="F96">
-        <v>-5.720029483180209</v>
+        <v>-6.88772516702549</v>
       </c>
       <c r="G96">
-        <v>-11.70482493981306</v>
+        <v>-8.848820163478342</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.9821578855582823</v>
       </c>
       <c r="E97">
-        <v>-42.56155789432063</v>
+        <v>-41.5037425939209</v>
       </c>
       <c r="F97">
-        <v>-5.756654919527587</v>
+        <v>-5.967854644177946</v>
       </c>
       <c r="G97">
-        <v>-11.46684122132809</v>
+        <v>-9.092237584865748</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.111603885190491</v>
       </c>
       <c r="E98">
-        <v>-44.54705600179868</v>
+        <v>-42.3558496982852</v>
       </c>
       <c r="F98">
-        <v>-5.722691027645404</v>
+        <v>-5.788421981057545</v>
       </c>
       <c r="G98">
-        <v>-12.09772497178409</v>
+        <v>-10.09781058763785</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.259141149988138</v>
       </c>
       <c r="E99">
-        <v>-46.79148319608731</v>
+        <v>-45.683741469753</v>
       </c>
       <c r="F99">
-        <v>-5.865786526274602</v>
+        <v>-6.192047311541215</v>
       </c>
       <c r="G99">
-        <v>-12.17440055718519</v>
+        <v>-10.26502491952872</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.432655494070152</v>
       </c>
       <c r="E100">
-        <v>-48.67726317379795</v>
+        <v>-46.82769740272664</v>
       </c>
       <c r="F100">
-        <v>-5.855428620269997</v>
+        <v>-5.848910197177368</v>
       </c>
       <c r="G100">
-        <v>-12.63496922137665</v>
+        <v>-11.00321445864323</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.606746586913814</v>
       </c>
       <c r="E101">
-        <v>-49.91940887656141</v>
+        <v>-48.51390300244525</v>
       </c>
       <c r="F101">
-        <v>-5.702984995500207</v>
+        <v>-6.40654518100582</v>
       </c>
       <c r="G101">
-        <v>-12.79128333524704</v>
+        <v>-11.6369889652931</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.798906182105371</v>
       </c>
       <c r="E102">
-        <v>-51.94892714774952</v>
+        <v>-50.7672614795955</v>
       </c>
       <c r="F102">
-        <v>-6.23694813824256</v>
+        <v>-5.7672522237116</v>
       </c>
       <c r="G102">
-        <v>-12.5528927452887</v>
+        <v>-10.36339922310243</v>
       </c>
     </row>
   </sheetData>
